--- a/data/manufacturing/RAGFlow_피스톤헤드_가공_오류DB.xlsx
+++ b/data/manufacturing/RAGFlow_피스톤헤드_가공_오류DB.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="오류주의사항DB" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="오류주의사항DB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="출처" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'오류주의사항DB'!$A$1:$AA$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'오류주의사항DB'!$A$1:$AA$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA38"/>
+  <dimension ref="A1:AA46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5568,8 +5568,1076 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="120" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>PH-M-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>피스톤헤드</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>하부 체결면</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>내경</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Ø300(+0.052/0)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] Ø300 H7 구멍용 실린더 게이지 0점을 외측 마이크로미터로 맞춤</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Ø300(+0.052/0) 구멍을 재기 전 실린더 게이지 0점을 Ø300 세팅 링 대신 외측 마이크로미터 사이에서 맞췄다. 두 측정기 오차가 겹쳐 0.006mm 차이가 났고, 공차 폭 0.052mm의 10% 이상이 셋팅 오차로 들어갔다.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤 구멍 셋팅 기준 부적절</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>H7 같은 끼워맞춤 구멍은 같은 지름의 세팅 링(마스터 링)으로 실린더 게이지 0점을 맞추고, 세팅 링과 부품 온도를 같게 둔다.</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>실린더 게이지, Ø300 세팅 링</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>공차 폭 0.1mm 이하 구멍</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>일반공차 구멍은 제외</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>하부 체결면</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>측정기</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>피스톤 로드 끼움 불량</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>세팅 링으로 0점 재설정 후 재측정</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>HOLE, 하부 체결면, 내경, DIMENSION, Ø300(+0.052/0), 끼워맞춤 구멍 셋팅 기준 부적절, 하부 체결면, C4 측정기, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PH-M-038] 부품: 피스톤헤드. 부위: 하부 체결면. 형상: 하부 체결면(HOLE). 측정 특성: 내경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø300(+0.052/0). 오류 유형: C4 측정기. 중요도: 상. 오류: [정삭] Ø300 H7 구멍용 실린더 게이지 0점을 외측 마이크로미터로 맞춤. 상황: Ø300(+0.052/0) 구멍을 재기 전 실린더 게이지 0점을 Ø300 세팅 링 대신 외측 마이크로미터 사이에서 맞췄다. 두 측정기 오차가 겹쳐 0.006mm 차이가 났고, 공차 폭 0.052mm의 10% 이상이 셋팅 오차로 들어갔다. 원인: 끼워맞춤 구멍 셋팅 기준 부적절. 주의사항: H7 같은 끼워맞춤 구멍은 같은 지름의 세팅 링(마스터 링)으로 실린더 게이지 0점을 맞추고, 세팅 링과 부품 온도를 같게 둔다. 조치: 세팅 링으로 0점 재설정 후 재측정. 영향: 피스톤 로드 끼움 불량. 발생 단계: 정삭 후. 적용 조건: 공차 폭 0.1mm 이하 구멍. 제외·확인 조건: 일반공차 구멍은 제외. 측정기 후보: 실린더 게이지, Ø300 세팅 링. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="120" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>PH-M-039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>피스톤헤드</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>하부 체결면</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>내경</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Ø300(+0.052/0)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 구멍 공차 (+0.052/0)의 하한을 놓쳐 299.99를 합격 처리</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Ø300(+0.052/0) 구멍은 300.000~300.052만 합격인데 '300 근처면 합격'으로 보고 299.990을 합격 처리했다. 피스톤 로드 맞춤 돌기(최대 300.000)가 들어가지 않았다.</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>편측 공차 하한 해석 오류</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>구멍의 (+/0) 공차는 기준치수가 하한이다. 화면 허용 범위(최소~최대)를 숫자로 확인하고, 하한 미만은 불합격이다.</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>실린더 게이지</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>(+/0) 편측 공차 구멍</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>하부 체결면</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>도면 해석</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>조립 불가, 재가공</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>허용 범위로 재판정, 재보링</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>HOLE, 하부 체결면, 내경, DIMENSION, Ø300(+0.052/0), 편측 공차 하한 해석 오류, 하부 체결면, C3 도면 해석, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PH-M-039] 부품: 피스톤헤드. 부위: 하부 체결면. 형상: 하부 체결면(HOLE). 측정 특성: 내경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø300(+0.052/0). 오류 유형: C3 도면 해석. 중요도: 상. 오류: [정삭] 구멍 공차 (+0.052/0)의 하한을 놓쳐 299.99를 합격 처리. 상황: Ø300(+0.052/0) 구멍은 300.000~300.052만 합격인데 '300 근처면 합격'으로 보고 299.990을 합격 처리했다. 피스톤 로드 맞춤 돌기(최대 300.000)가 들어가지 않았다. 원인: 편측 공차 하한 해석 오류. 주의사항: 구멍의 (+/0) 공차는 기준치수가 하한이다. 화면 허용 범위(최소~최대)를 숫자로 확인하고, 하한 미만은 불합격이다. 조치: 허용 범위로 재판정, 재보링. 영향: 조립 불가, 재가공. 발생 단계: 정삭 후. 적용 조건: (+/0) 편측 공차 구멍. 제외·확인 조건: 없음. 측정기 후보: 실린더 게이지. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="120" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>PH-M-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>피스톤헤드</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>하부 체결면</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>내경</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Ø300(+0.052/0)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>공정</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>[중삭] Ø300 끼워맞춤 구멍 중삭 후 테이퍼를 확인하지 않고 정삭</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>보링바가 길게 나와 휘면서 Ø300 구멍이 안쪽으로 0.08mm 좁아졌는데, 입구만 재고 정삭으로 넘겼다. 정삭 여유가 한쪽에서 모자라 안쪽 끝이 하한을 넘지 못했다.</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>중삭 구멍 깊이 방향 확인 누락</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤 구멍은 중삭 후 입구·중간·안쪽 3단면을 재서 테이퍼를 확인하고, 테이퍼가 정삭 여유(0.5mm)의 1/3을 넘으면 보링바 돌출을 줄여 다시 중삭한다.</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>실린더 게이지</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>깊이가 있는 끼워맞춤 구멍 중삭 후</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>얕은 구멍은 입구·안쪽 2단면</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>하부 체결면</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>공정 추세·시삭</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>중삭 후</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>정삭 후 테이퍼 잔존, 끼워맞춤 불량</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>보링 조건 수정 후 재중삭</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>HOLE, 하부 체결면, 내경, DIMENSION, Ø300(+0.052/0), 중삭 구멍 깊이 방향 확인 누락, 하부 체결면, C12 공정 추세·시삭, 중삭 후</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PH-M-040] 부품: 피스톤헤드. 부위: 하부 체결면. 형상: 하부 체결면(HOLE). 측정 특성: 내경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø300(+0.052/0). 오류 유형: C12 공정 추세·시삭. 중요도: 중. 오류: [중삭] Ø300 끼워맞춤 구멍 중삭 후 테이퍼를 확인하지 않고 정삭. 상황: 보링바가 길게 나와 휘면서 Ø300 구멍이 안쪽으로 0.08mm 좁아졌는데, 입구만 재고 정삭으로 넘겼다. 정삭 여유가 한쪽에서 모자라 안쪽 끝이 하한을 넘지 못했다. 원인: 중삭 구멍 깊이 방향 확인 누락. 주의사항: 끼워맞춤 구멍은 중삭 후 입구·중간·안쪽 3단면을 재서 테이퍼를 확인하고, 테이퍼가 정삭 여유(0.5mm)의 1/3을 넘으면 보링바 돌출을 줄여 다시 중삭한다. 조치: 보링 조건 수정 후 재중삭. 영향: 정삭 후 테이퍼 잔존, 끼워맞춤 불량. 발생 단계: 중삭 후. 적용 조건: 깊이가 있는 끼워맞춤 구멍 중삭 후. 제외·확인 조건: 얕은 구멍은 입구·안쪽 2단면. 측정기 후보: 실린더 게이지. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>PH-M-041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>피스톤헤드</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>하부 체결면</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>내경</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Ø300(+0.052/0)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 무거운 피스톤헤드가 다 식기 전에 Ø300 구멍을 재서 합격 처리</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>질량이 큰 피스톤헤드는 정삭 후에도 내부 열이 오래 남는데, 표면만 만져보고 바로 Ø300을 재서 300.040(합격)으로 기록했다. 다음 날 재측정하니 300.028이었다.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>대형 부품 온도 안정 시간 부족</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>대형 부품은 측정실에 충분히 두어 온도를 맞추고(표면 온도계로 확인), 끼워맞춤 구멍은 온도와 함께 기록한다.</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>실린더 게이지, 표면 온도계</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>정삭 직후 대형 부품</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>온도 안정 후 측정한 경우 제외</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>하부 체결면</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>온도·환경</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>성적서 값과 실제 치수 차이</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>온도 안정 후 재측정</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>HOLE, 하부 체결면, 내경, DIMENSION, Ø300(+0.052/0), 대형 부품 온도 안정 시간 부족, 하부 체결면, C9 온도·환경, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PH-M-041] 부품: 피스톤헤드. 부위: 하부 체결면. 형상: 하부 체결면(HOLE). 측정 특성: 내경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø300(+0.052/0). 오류 유형: C9 온도·환경. 중요도: 중. 오류: [정삭] 무거운 피스톤헤드가 다 식기 전에 Ø300 구멍을 재서 합격 처리. 상황: 질량이 큰 피스톤헤드는 정삭 후에도 내부 열이 오래 남는데, 표면만 만져보고 바로 Ø300을 재서 300.040(합격)으로 기록했다. 다음 날 재측정하니 300.028이었다. 원인: 대형 부품 온도 안정 시간 부족. 주의사항: 대형 부품은 측정실에 충분히 두어 온도를 맞추고(표면 온도계로 확인), 끼워맞춤 구멍은 온도와 함께 기록한다. 조치: 온도 안정 후 재측정. 영향: 성적서 값과 실제 치수 차이. 발생 단계: 정삭 후. 적용 조건: 정삭 직후 대형 부품. 제외·확인 조건: 온도 안정 후 측정한 경우 제외. 측정기 후보: 실린더 게이지, 표면 온도계. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="120" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>PH-M-042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>피스톤헤드</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>SLOT</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>링 홈</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>R2 (= Ra 0.8)</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 링 홈 측면 조도(R2)를 홈 바닥에서 재서 합격 처리</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>폭 22 링 홈 측면(R2 = Ra 0.8)에 조도계 촉침이 들어가지 않아 홈 바닥을 재서 Ra 0.6으로 기록했다. 링이 닿는 면은 측면이며, 측면은 Ra 1.1이었다.</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>조도 측정 부위 오류</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>링 홈은 링이 닿는 측면이 조도 관리면이다. 촉침이 안 들어가면 측면용 촉침(옆 방향)을 쓰거나 레플리카로 본을 떠서 잰다.</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계(측면용 촉침), 레플리카</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>좁은 홈 측면 조도 측정</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>홈 바닥 조도 요구가 따로 있으면 별도 측정</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>링 홈</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>측정 위치</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>링 마모·가스 누설</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>측면 재측정</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>SLOT, 링 홈, 표면 거칠기, SURFACE_ROUGHNESS, R2 (= Ra 0.8), 조도 측정 부위 오류, 링 홈, C1 측정 위치, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PH-M-042] 부품: 피스톤헤드. 부위: 링 홈. 형상: 링 홈(SLOT). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R2 (= Ra 0.8). 오류 유형: C1 측정 위치. 중요도: 상. 오류: [정삭] 링 홈 측면 조도(R2)를 홈 바닥에서 재서 합격 처리. 상황: 폭 22 링 홈 측면(R2 = Ra 0.8)에 조도계 촉침이 들어가지 않아 홈 바닥을 재서 Ra 0.6으로 기록했다. 링이 닿는 면은 측면이며, 측면은 Ra 1.1이었다. 원인: 조도 측정 부위 오류. 주의사항: 링 홈은 링이 닿는 측면이 조도 관리면이다. 촉침이 안 들어가면 측면용 촉침(옆 방향)을 쓰거나 레플리카로 본을 떠서 잰다. 조치: 측면 재측정. 영향: 링 마모·가스 누설. 발생 단계: 정삭 후. 적용 조건: 좁은 홈 측면 조도 측정. 제외·확인 조건: 홈 바닥 조도 요구가 따로 있으면 별도 측정. 측정기 후보: 표면조도계(측면용 촉침), 레플리카. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="120" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>PH-M-043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>피스톤헤드</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>PLANE</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>하부 체결면</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>R1 (= Ra 1.6)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 하부 체결면 조도를 볼트 구멍 가장자리에 걸쳐 재서 값이 큼</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>R1(Ra 1.6) 하부 체결면을 재면서 촉침 이동 구간이 Ø39 볼트 구멍 모따기에 걸려 Ra 3.2로 불합격 처리했다. 구멍을 피해 다시 재니 Ra 1.2였다.</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>측정 구간 선정 오류</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>평가 길이(약 4mm) 전체가 평평한 가공면 위에 있도록 구멍·모서리에서 떨어진 위치를 고른다. 위치를 2곳 이상 바꿔 잰다.</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>구멍이 많은 체결면 조도</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>하부 체결면</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>측정 위치</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>불필요한 재가공</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>위치를 바꿔 재측정</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>PLANE, 하부 체결면, 표면 거칠기, SURFACE_ROUGHNESS, R1 (= Ra 1.6), 측정 구간 선정 오류, 하부 체결면, C1 측정 위치, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PH-M-043] 부품: 피스톤헤드. 부위: 하부 체결면. 형상: 하부 체결면(PLANE). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R1 (= Ra 1.6). 오류 유형: C1 측정 위치. 중요도: 중. 오류: [정삭] 하부 체결면 조도를 볼트 구멍 가장자리에 걸쳐 재서 값이 큼. 상황: R1(Ra 1.6) 하부 체결면을 재면서 촉침 이동 구간이 Ø39 볼트 구멍 모따기에 걸려 Ra 3.2로 불합격 처리했다. 구멍을 피해 다시 재니 Ra 1.2였다. 원인: 측정 구간 선정 오류. 주의사항: 평가 길이(약 4mm) 전체가 평평한 가공면 위에 있도록 구멍·모서리에서 떨어진 위치를 고른다. 위치를 2곳 이상 바꿔 잰다. 조치: 위치를 바꿔 재측정. 영향: 불필요한 재가공. 발생 단계: 정삭 후. 적용 조건: 구멍이 많은 체결면 조도. 제외·확인 조건: 없음. 측정기 후보: 표면조도계. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="120" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>PH-M-044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>피스톤헤드</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>진원도</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>ROUNDNESS</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>○ 0.001</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>[공통] OCR이 진원도 0.001을 0.01로 읽은 값으로 판정</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>개정 도면의 외경 진원도 ○0.001을 OCR이 0.01로 읽었고, 관리자 확인 전 값으로 진원도 0.006을 합격 처리했다.</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>OCR 값 미확인</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>기하공차 값은 관리자 확정 값으로만 판정한다. 0.001처럼 0이 여러 개인 값은 원본 도면과 한 번 더 대조한다.</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>진원도 측정기</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>OCR로 읽은 기하공차</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>관리자 확정 후 값은 제외</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>도면 해석</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V45" s="6" t="inlineStr">
+        <is>
+          <t>가공 공통</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>진원도 불량 합격 처리</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>확정 값으로 재판정</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>0.001 → 0.01 처럼 0을 빠뜨리는 오인식</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 외경, 진원도, ROUNDNESS, ○ 0.001, OCR 값 미확인, 외경, C3 도면 해석, 가공 공통</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PH-M-044] 부품: 피스톤헤드. 부위: 외경. 형상: 외경(SHAFT). 측정 특성: 진원도. 공차·검사 유형: ROUNDNESS. 도면 표기 예시: ○ 0.001. 오류 유형: C3 도면 해석. 중요도: 중. 오류: [공통] OCR이 진원도 0.001을 0.01로 읽은 값으로 판정. 상황: 개정 도면의 외경 진원도 ○0.001을 OCR이 0.01로 읽었고, 관리자 확인 전 값으로 진원도 0.006을 합격 처리했다. 원인: OCR 값 미확인. 주의사항: 기하공차 값은 관리자 확정 값으로만 판정한다. 0.001처럼 0이 여러 개인 값은 원본 도면과 한 번 더 대조한다. 조치: 확정 값으로 재판정. 영향: 진원도 불량 합격 처리. 발생 단계: 가공 공통. 적용 조건: OCR로 읽은 기하공차. 제외·확인 조건: 관리자 확정 후 값은 제외. 측정기 후보: 진원도 측정기. OCR 참고: 0.001 → 0.01 처럼 0을 빠뜨리는 오인식. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="120" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>PH-M-045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>피스톤헤드</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>SLOT</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>링 홈</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>R2 (= Ra 0.8)</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>[공통] 비교용 조도 표준편을 손으로 문질러 Ra 0.8 면을 판정</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>링 홈 측면(R2 = Ra 0.8)을 조도계 없이 비교용 표준편과 손톱으로 비교해 합격으로 기록했다. Ra 1.6 이하 면은 촉감으로 구분이 어렵다.</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>정밀 조도의 감각 판정</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>비교용 표준편은 Ra 3.2 이상 거친 면의 대략 확인용이다. Ra 1.6 이하 지정 면은 표면조도계로 재서 숫자로 기록한다.</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계, 비교용 표준편(참고용)</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Ra 1.6 이하 지정 면</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Ra 3.2 이상 거친 면은 표준편 비교 허용</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>링 홈</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>측정기</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="V46" s="6" t="inlineStr">
+        <is>
+          <t>가공 공통</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>조도 불량 유출</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>조도계로 재측정</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>SLOT, 링 홈, 표면 거칠기, SURFACE_ROUGHNESS, R2 (= Ra 0.8), 정밀 조도의 감각 판정, 링 홈, C4 측정기, 가공 공통</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PH-M-045] 부품: 피스톤헤드. 부위: 링 홈. 형상: 링 홈(SLOT). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R2 (= Ra 0.8). 오류 유형: C4 측정기. 중요도: 하. 오류: [공통] 비교용 조도 표준편을 손으로 문질러 Ra 0.8 면을 판정. 상황: 링 홈 측면(R2 = Ra 0.8)을 조도계 없이 비교용 표준편과 손톱으로 비교해 합격으로 기록했다. Ra 1.6 이하 면은 촉감으로 구분이 어렵다. 원인: 정밀 조도의 감각 판정. 주의사항: 비교용 표준편은 Ra 3.2 이상 거친 면의 대략 확인용이다. Ra 1.6 이하 지정 면은 표면조도계로 재서 숫자로 기록한다. 조치: 조도계로 재측정. 영향: 조도 불량 유출. 발생 단계: 가공 공통. 적용 조건: Ra 1.6 이하 지정 면. 제외·확인 조건: Ra 3.2 이상 거친 면은 표준편 비교 허용. 측정기 후보: 표면조도계, 비교용 표준편(참고용). 우선순위: 3(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA38"/>
+  <autoFilter ref="A1:AA46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5580,7 +6648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6234,6 +7302,142 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PH-M-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PH_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[정삭] Ø300 H7 구멍용 실린더 게이지 0점을 외측 마이크로미터로 맞춤</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PH-M-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PH_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[정삭] 구멍 공차 (+0.052/0)의 하한을 놓쳐 299.99를 합격 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PH-M-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PH_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[중삭] Ø300 끼워맞춤 구멍 중삭 후 테이퍼를 확인하지 않고 정삭</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PH-M-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PH_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[정삭] 무거운 피스톤헤드가 다 식기 전에 Ø300 구멍을 재서 합격 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PH-M-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PH_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[정삭] 링 홈 측면 조도(R2)를 홈 바닥에서 재서 합격 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PH-M-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PH_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[정삭] 하부 체결면 조도를 볼트 구멍 가장자리에 걸쳐 재서 값이 큼</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PH-M-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PH_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[공통] OCR이 진원도 0.001을 0.01로 읽은 값으로 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PH-M-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PH_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[공통] 비교용 조도 표준편을 손으로 문질러 Ra 0.8 면을 판정</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
